--- a/stories/arbres/ATOM-VIV.ANI.001-03.xlsx
+++ b/stories/arbres/ATOM-VIV.ANI.001-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Emma marche avec maman. Elles suivent le chemin des prés. L'herbe est haute. Un chien arrive. Le chien aboie. Ouaf ouaf. Maman dit : le chien aboie. C'est le cri. Emma nomme l'animal. Elle dit : un chien. Un chat saute d'un muret. Le chat miaule. Miaou. Une vache mange l'herbe. La vache meugle. Meuh. Un coq est sur une barrière. Le coq chante. Cocorico. Un mouton s'approche. Le mouton bêle. Bêê. Un canard nage dans le fossé. Le canard cancane. Coin coin. Parce qu'Emma entend le cri, elle peut nommer l'animal. Maman dit : chaque animal a un cri. Emma répète le nom de l'animal. Elle dit le cri. Parce qu'elle a nommé, maman sourit. Emma touche l'herbe. Elle dit encore : le mouton bêle.</t>
+          <t>Emma marche avec maman. Elles suivent le chemin des prés. L'herbe est haute. Un chien arrive. Le chien aboie. Ouaf ouaf. Le chien aboie. C'est le cri. Emma nomme l'animal. Un chien. Un chat saute d'un muret. Le chat miaule. Miaou. Une vache mange l'herbe. La vache meugle. Meuh. Un coq est sur une barrière. Le coq chante. Cocorico. Un mouton s'approche. Le mouton bêle. Bêê. Un canard nage dans le fossé. Le canard cancane. Coin coin. Parce qu'Emma entend le cri, elle peut nommer l'animal. Chaque animal a un cri. Emma répète le nom de l'animal. Elle dit le cri. Parce qu'elle a nommé, maman sourit. Emma touche l'herbe. Elle dit encore : le mouton bêle.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,17 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Emma marche avec maman. Elles suivent le chemin des prés. L'herbe est haute. Un chien arrive. Le chien aboie. Ouaf ouaf.
+maman|Le chien aboie. C'est le cri.
+narrateur|Emma nomme l'animal.
+narrateur|Un chien.
+narrateur|Un chat saute d'un muret. Le chat miaule. Miaou. Une vache mange l'herbe. La vache meugle. Meuh. Un coq est sur une barrière. Le coq chante. Cocorico. Un mouton s'approche. Le mouton bêle. Bêê. Un canard nage dans le fossé. Le canard cancane. Coin coin. Parce qu'Emma entend le cri, elle peut nommer l'animal.
+maman|Chaque animal a un cri.
+narrateur|Emma répète le nom de l'animal. Elle dit le cri. Parce qu'elle a nommé, maman sourit. Emma touche l'herbe. Elle dit encore : le mouton bêle.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1496,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Le mouton fait bêê. Quel est son cri ?</t>
         </is>
       </c>
     </row>
@@ -1637,6 +1669,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Emma a nommé l'animal. Elle a dit le cri. Maman était là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1799,6 +1836,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Emma donne la main à maman. Le chemin est calme.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1961,6 +2003,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1979,7 +2026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1996,6 +2043,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-VIV.ANI.001-03.xlsx
+++ b/stories/arbres/ATOM-VIV.ANI.001-03.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1316,6 +1321,11 @@
 narrateur|Emma répète le nom de l'animal. Elle dit le cri. Parce qu'elle a nommé, maman sourit. Emma touche l'herbe. Elle dit encore : le mouton bêle.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc,chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1503,6 +1513,7 @@
           <t>narrateur|Le mouton fait bêê. Quel est son cri ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1674,6 +1685,7 @@
           <t>narrateur|Emma a nommé l'animal. Elle a dit le cri. Maman était là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1841,6 +1853,7 @@
           <t>narrateur|Emma donne la main à maman. Le chemin est calme.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2008,6 +2021,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2026,7 +2040,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2050,6 +2064,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2064,7 +2092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2251,6 +2279,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-VIV.ANI.001-03.xlsx
+++ b/stories/arbres/ATOM-VIV.ANI.001-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Les cris du chemin des prés</t>
+          <t>Le meuh derrière la haie</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Amir veut la vache du pré. Le meuh est loin, puis plus près. La barrière est fermée. Ils écoutent par la haie.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Emma marche avec maman. Elles suivent le chemin des prés. L'herbe est haute. Un chien arrive. Le chien aboie. Ouaf ouaf. Le chien aboie. C'est le cri. Emma nomme l'animal. Un chien. Un chat saute d'un muret. Le chat miaule. Miaou. Une vache mange l'herbe. La vache meugle. Meuh. Un coq est sur une barrière. Le coq chante. Cocorico. Un mouton s'approche. Le mouton bêle. Bêê. Un canard nage dans le fossé. Le canard cancane. Coin coin. Parce qu'Emma entend le cri, elle peut nommer l'animal. Chaque animal a un cri. Emma répète le nom de l'animal. Elle dit le cri. Parce qu'elle a nommé, maman sourit. Emma touche l'herbe. Elle dit encore : le mouton bêle.</t>
+          <t>Le chemin des prés sent le foin coupé. Des brins jaunes collent aux chaussettes. Un papillon poussiéreux se pose sur une tige. La terre du sentier est sèche et claire. Tu sens le foin, Amir ? Oui. Il pique le nez. Un meuh arrive, tout loin. La vache ! Tu l'as entendue ? Je veux la voir. En ce moment, Amir accélère un peu. Le sentier monte entre deux buissons. Le meuh revient, plus fort. Elle est près. On continue ? Oui. Une barrière de bois barre le chemin. Le loquet est fermé, tout gris. On ne passe pas. La barrière est fermée. On reste de ce côté. Amir pose les mains sur le bois chaud. Le bois sent la sève sèche. Derrière, une haie d'aubépine tremble. On écoute par la haie ? Oui. Ils se baissent près des feuilles. Une épine accroche le pull d'Amir. Maman la décroche tout doux. Le meuh passe à travers les feuilles. Meuh. La vache meugle. Amir colle l'oreille vers la haie. Un œil brun cligne entre les branches. Une tache blanche marque le poil. Elle mâche. On la regarde par les feuilles. Le foin coupé pique encore les chevilles. Amir ne touche pas le loquet.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Emma marche avec maman. Elles suivent le chemin des prés. L'herbe est haute. Un chien arrive. Le chien aboie. Ouaf ouaf. Maman dit : le chien aboie. C'est le cri. Emma &lt;emphasis level="moderate"&gt;nom&lt;/emphasis&gt;me l'animal. Elle dit : un chien. Un chat saute d'un muret. Le chat miaule. Miaou. Une vache mange l'herbe. La vache meugle. Meuh. Un coq est sur une barrière. Le coq chante. Cocorico. Un mouton s'approche. Le mouton bêle. Bêê. Un canard nage dans le fossé. Le canard cancane. Coin coin. Parce qu'Emma entend le cri, elle peut nommer l'animal. Maman dit : chaque animal a un cri. Emma répète le nom de l'animal. Elle dit le cri. Parce qu'elle a nommé, maman sourit. Emma touche l'herbe. Elle dit encore : le mouton bêle.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le chemin des prés sent le foin coupé. Des brins jaunes collent aux chaussettes. Un papillon poussiéreux se pose sur une tige. La terre du sentier est sèche et claire. Tu sens le foin, Amir ? Oui. Il pique le nez. Un meuh arrive, tout loin. La vache ! Tu l'as entendue ? Je veux la voir. En ce moment, Amir accélère un peu. Le sentier monte entre deux buissons. Le meuh revient, plus fort. Elle est près. On continue ? Oui. Une barrière de bois barre le chemin. Le loquet est fermé, tout gris. On ne passe pas. La barrière est fermée. On reste de ce côté. Amir pose les mains sur le bois chaud. Le bois sent la sève sèche. Derrière, une haie d'aubépine tremble. On écoute par la haie ? Oui. Ils se baissent près des feuilles. Une épine accroche le pull d'Amir. Maman la décroche tout doux. Le meuh passe à travers les feuilles. Meuh. La vache meugle. Amir colle l'oreille vers la haie. Un œil brun cligne entre les branches. Une tache blanche marque le poil. Elle mâche. On la regarde par les feuilles. Le foin coupé pique encore les chevilles. Amir ne touche pas le loquet.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1240,7 +1252,7 @@
         <v>0.92</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,13 +1324,46 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Emma marche avec maman. Elles suivent le chemin des prés. L'herbe est haute. Un chien arrive. Le chien aboie. Ouaf ouaf.
-maman|Le chien aboie. C'est le cri.
-narrateur|Emma nomme l'animal.
-narrateur|Un chien.
-narrateur|Un chat saute d'un muret. Le chat miaule. Miaou. Une vache mange l'herbe. La vache meugle. Meuh. Un coq est sur une barrière. Le coq chante. Cocorico. Un mouton s'approche. Le mouton bêle. Bêê. Un canard nage dans le fossé. Le canard cancane. Coin coin. Parce qu'Emma entend le cri, elle peut nommer l'animal.
-maman|Chaque animal a un cri.
-narrateur|Emma répète le nom de l'animal. Elle dit le cri. Parce qu'elle a nommé, maman sourit. Emma touche l'herbe. Elle dit encore : le mouton bêle.</t>
+          <t>narrateur|Le chemin des prés sent le foin coupé.
+narrateur|Des brins jaunes collent aux chaussettes.
+narrateur|Un papillon poussiéreux se pose sur une tige.
+narrateur|La terre du sentier est sèche et claire.
+maman|Tu sens le foin, Amir ?
+enfant-m|Oui.
+enfant-m|Il pique le nez.
+narrateur|Un meuh arrive, tout loin.
+enfant-m|La vache !
+maman|Tu l'as entendue ?
+enfant-m|Je veux la voir.
+narrateur|En ce moment, Amir accélère un peu.
+narrateur|Le sentier monte entre deux buissons.
+narrateur|Le meuh revient, plus fort.
+enfant-m|Elle est près.
+maman|On continue ?
+enfant-m|Oui.
+narrateur|Une barrière de bois barre le chemin.
+narrateur|Le loquet est fermé, tout gris.
+enfant-m|On ne passe pas.
+maman|La barrière est fermée.
+maman|On reste de ce côté.
+narrateur|Amir pose les mains sur le bois chaud.
+narrateur|Le bois sent la sève sèche.
+narrateur|Derrière, une haie d'aubépine tremble.
+maman|On écoute par la haie ?
+enfant-m|Oui.
+narrateur|Ils se baissent près des feuilles.
+narrateur|Une épine accroche le pull d'Amir.
+narrateur|Maman la décroche tout doux.
+narrateur|Le meuh passe à travers les feuilles.
+enfant-m|Meuh.
+maman|La vache meugle.
+narrateur|Amir colle l'oreille vers la haie.
+narrateur|Un œil brun cligne entre les branches.
+narrateur|Une tache blanche marque le poil.
+enfant-m|Elle mâche.
+maman|On la regarde par les feuilles.
+narrateur|Le foin coupé pique encore les chevilles.
+narrateur|Amir ne touche pas le loquet.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1350,12 +1395,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Le mouton fait bêê. Quel est son cri ?</t>
+          <t>Amir entend meuh. Quel est le cri de la vache ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Le mouton fait bêê. Quel est son &lt;emphasis level="moderate"&gt;cri&lt;/emphasis&gt; ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Amir entend meuh. Quel est le cri de la vache ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1365,12 +1410,12 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>bêê</t>
+          <t>meuh</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>bêê | il bêle | le cri | mouton | un animal</t>
+          <t>meuh | elle meugle | meugle | le cri | la vache</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1385,7 +1430,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Emma nomme l'animal. Elle dit le cri. Que dit-elle ?</t>
+          <t>La vache meugle. Quel est le cri ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1434,7 +1479,7 @@
         <v>0.86</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1510,10 +1555,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Le mouton fait bêê. Quel est son cri ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Amir entend meuh.
+narrateur|Quel est le cri de la vache ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1538,12 +1583,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Emma a nommé l'animal. Elle a dit le cri. Maman était là.</t>
+          <t>La vache lève le museau derrière la haie. Un brin de foin paille son poil. Je la vois. Merci d'être resté de ce côté. On écoute par la haie. Elle meugle. Oui. Meuh. La vache mâche tout lentement. Sa cloche fait un petit toc. Amir ne pousse pas le loquet. On reste ici ? Oui. Une feuille d'aubépine chatouille son oreille. Le meuh revient, tout proche.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Emma a &lt;emphasis level="moderate"&gt;nom&lt;/emphasis&gt;mé l'animal. Elle a dit le cri. Maman était là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>La vache lève le museau derrière la haie. Un brin de foin paille son poil. Je la vois. Merci d'être resté de ce côté. On écoute par la haie. Elle meugle. Oui. Meuh. La vache mâche tout lentement. Sa cloche fait un petit toc. Amir ne pousse pas le loquet. On reste ici ? Oui. Une feuille d'aubépine chatouille son oreille. Le meuh revient, tout proche.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1606,7 +1651,7 @@
         <v>0.92</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1682,10 +1727,23 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Emma a nommé l'animal. Elle a dit le cri. Maman était là.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|La vache lève le museau derrière la haie.
+narrateur|Un brin de foin paille son poil.
+enfant-m|Je la vois.
+maman|Merci d'être resté de ce côté.
+maman|On écoute par la haie.
+enfant-m|Elle meugle.
+maman|Oui.
+maman|Meuh.
+narrateur|La vache mâche tout lentement.
+narrateur|Sa cloche fait un petit toc.
+narrateur|Amir ne pousse pas le loquet.
+maman|On reste ici ?
+enfant-m|Oui.
+narrateur|Une feuille d'aubépine chatouille son oreille.
+narrateur|Le meuh revient, tout proche.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1710,12 +1768,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Emma donne la main à maman. Le chemin est calme.</t>
+          <t>Le papillon repart vers le foin. Amir garde les mains sur le bois. Elle est grande. Tu voulais la vache. Elle est derrière la haie. Un nuage passe sur le pré. L'œil brun cligne encore. La cloche fait toc, toc. Meuh. C'est son cri. Le sentier sent encore le foin coupé. Amir recule d'un pas, tout seul. Tu as bien écouté. Un brin de foin reste collé au pull. Amir le souffle vers le pré. Meuh encore. Elle est toujours là.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Emma donne la &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt; à maman. Le chemin est calme.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le papillon repart vers le foin. Amir garde les mains sur le bois. Elle est grande. Tu voulais la vache. Elle est derrière la haie. Un nuage passe sur le pré. L'œil brun cligne encore. La cloche fait toc, toc. Meuh. C'est son cri. Le sentier sent encore le foin coupé. Amir recule d'un pas, tout seul. Tu as bien écouté. Un brin de foin reste collé au pull. Amir le souffle vers le pré. Meuh encore. Elle est toujours là.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1778,7 +1836,7 @@
         <v>0.92</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1850,10 +1908,25 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Emma donne la main à maman. Le chemin est calme.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Le papillon repart vers le foin.
+narrateur|Amir garde les mains sur le bois.
+enfant-m|Elle est grande.
+maman|Tu voulais la vache.
+maman|Elle est derrière la haie.
+narrateur|Un nuage passe sur le pré.
+narrateur|L'œil brun cligne encore.
+narrateur|La cloche fait toc, toc.
+enfant-m|Meuh.
+maman|C'est son cri.
+narrateur|Le sentier sent encore le foin coupé.
+narrateur|Amir recule d'un pas, tout seul.
+maman|Tu as bien écouté.
+narrateur|Un brin de foin reste collé au pull.
+narrateur|Amir le souffle vers le pré.
+enfant-m|Meuh encore.
+maman|Elle est toujours là.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1878,12 +1951,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>La barrière reste fermée, tiède. Amir prend la main de maman. Je l'ai entendue. Oui. Le meuh passe encore à travers les feuilles.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>La barrière reste fermée, tiède. Amir prend la main de maman. Je l'ai entendue. Oui. Le meuh passe encore à travers les feuilles.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1939,14 +2012,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.88</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2018,10 +2091,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|La barrière reste fermée, tiède.
+narrateur|Amir prend la main de maman.
+enfant-m|Je l'ai entendue.
+maman|Oui.
+narrateur|Le meuh passe encore à travers les feuilles.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2040,7 +2116,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2078,6 +2154,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-VIV.ANI.001-03.xlsx
+++ b/stories/arbres/ATOM-VIV.ANI.001-03.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>chemin des prés</t>
+          <t>chemin des prés, après la coupe du foin</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Emma, maman</t>
+          <t>Amir, maman</t>
         </is>
       </c>
     </row>
